--- a/bom/order_bom.xlsx
+++ b/bom/order_bom.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Variant A (Reichelt)" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Variant A+B (Mouser)" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Variant A (Mouser)" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Variant B (Reichelt)" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Variant B (Mouser)" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t xml:space="preserve">Variants: (https://github.com/MS71/RTK1010Board)see </t>
   </si>
@@ -155,6 +156,15 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.reichelt.de/wifi-modul-802-11-bt-2-4-2-5ghz-150mb-s-esp32s2wroveri4-p311738.html?search=ESP32+S2+w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">649-10118194-0001LF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB Connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://eu.mouser.com/ProductDetail/Amphenol-FCI/10118194-0001LF?qs=Ywefl8B65e4FIdY8OWfRQA%3D%3D&amp;countryCode=DE&amp;currencyCode=EUR</t>
   </si>
 </sst>
 </file>
@@ -311,7 +321,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="100.8"/>
   </cols>
@@ -414,7 +424,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="Variants: (https://github.com/MS71/RTK1010Board)"/>
+    <hyperlink ref="A1" r:id="rId1" display="Variants: (https://github.com/MS71/RTK1010Board)see "/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -432,7 +442,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="26.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="41.22"/>
@@ -563,7 +573,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.17"/>
@@ -621,7 +631,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.42"/>
@@ -659,6 +669,78 @@
       </c>
       <c r="D3" s="0" t="s">
         <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="103.19"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
